--- a/site/Entra-ID-Zendesk-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Zendesk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,7 +551,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -567,6 +567,556 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>User &amp; Access Management Features</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01KT6TBPVHSVHHKWY67Z0DSDBE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6TBPVHSVHHKWY67Z0DSDBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Entra ID</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KT6V74NYNR6Y2WEYDMWZKXK1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6V74NYNR6Y2WEYDMWZKXK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>User Configuration</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KT645Z6F5184XKG1HJ1R57QS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT645Z6F5184XKG1HJ1R57QS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Select Source Application</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KT6SENNW157B9D9PEHCG3VNH</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6SENNW157B9D9PEHCG3VNH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>User Configuration</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KT64NVVAEW5NCVBYRAX7NG85</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT64NVVAEW5NCVBYRAX7NG85</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KT64T7D13E5K24HB1N923E98</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT64T7D13E5K24HB1N923E98</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Zendesk Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KT64TBWZ9MVA03QZTR6KTEXX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT64TBWZ9MVA03QZTR6KTEXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>User Management</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KT64XJPJD2M641DSMDT3279C</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT64XJPJD2M641DSMDT3279C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Match Users Between Entra ID and Zendesk</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KT64Y4V285ZVTZBRTAYT331A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT64Y4V285ZVTZBRTAYT331A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Safeguard Limits</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KT655C4SFRS3PBNHP0H508A4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT655C4SFRS3PBNHP0H508A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Entra ID User to Zendesk User</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KT65MWF5RTVM1DDGRD0PGC1Z</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT65MWF5RTVM1DDGRD0PGC1Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KT6A95YE1NDSVY2QX1DRBAWP</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6A95YE1NDSVY2QX1DRBAWP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PII Attributes</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KT6SGR75KXD47Z8E3W29KWT1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6SGR75KXD47Z8E3W29KWT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KT6AHSW9KV380YR9WAXJVDA3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6AHSW9KV380YR9WAXJVDA3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Advance Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KT6AHWYRCMPWPK0CFJZAQ2QN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6AHWYRCMPWPK0CFJZAQ2QN</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RollOut Configurations</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KT6SJ2R0YVAR6GYF3FEV2SEC</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6SJ2R0YVAR6GYF3FEV2SEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Source Filter</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KT6BN63Q9JP3BFM0NRWMQZ0T</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6BN63Q9JP3BFM0NRWMQZ0T</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KT6C2D4SHAAWSY0FS84YRZ7W</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6C2D4SHAAWSY0FS84YRZ7W</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Operational Settings</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KT6C3EKMNT15E2GRN543D237</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6C3EKMNT15E2GRN543D237</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Insights Settings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KT6CJQCS03KJD036GY6YNQJ7</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6CJQCS03KJD036GY6YNQJ7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Logging Settings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KT6CZ6SK0CR6SJ6662M8E2VW</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6CZ6SK0CR6SJ6662M8E2VW</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>

--- a/site/Entra-ID-Zendesk-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Zendesk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,95 +903,95 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RollOut Configurations</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KT6SJ2R0YVAR6GYF3FEV2SEC</t>
+          <t>h_01KT6BN63Q9JP3BFM0NRWMQZ0T</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6SJ2R0YVAR6GYF3FEV2SEC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6BN63Q9JP3BFM0NRWMQZ0T</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KT6BN63Q9JP3BFM0NRWMQZ0T</t>
+          <t>h_01KT6C2D4SHAAWSY0FS84YRZ7W</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6BN63Q9JP3BFM0NRWMQZ0T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6C2D4SHAAWSY0FS84YRZ7W</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KT6C2D4SHAAWSY0FS84YRZ7W</t>
+          <t>h_01KT6C3EKMNT15E2GRN543D237</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6C2D4SHAAWSY0FS84YRZ7W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6C3EKMNT15E2GRN543D237</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Insights Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KT6C3EKMNT15E2GRN543D237</t>
+          <t>h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6C3EKMNT15E2GRN543D237</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Insights Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
+          <t>h_01KT6CJQCS03KJD036GY6YNQJ7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6CJQCS03KJD036GY6YNQJ7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,98 +1023,76 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KT6CJQCS03KJD036GY6YNQJ7</t>
+          <t>h_01KT6CZ6SK0CR6SJ6662M8E2VW</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6CJQCS03KJD036GY6YNQJ7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6CZ6SK0CR6SJ6662M8E2VW</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KT6CZ6SK0CR6SJ6662M8E2VW</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KT6CZ6SK0CR6SJ6662M8E2VW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Zendesk-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
